--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.80041905418469</v>
+        <v>9.067568096305013</v>
       </c>
       <c r="D2" t="n">
-        <v>54.25372242032905</v>
+        <v>8.816229893303472</v>
       </c>
       <c r="E2" t="n">
-        <v>18.02622227559591</v>
+        <v>2.929261119784336</v>
       </c>
       <c r="F2" t="n">
-        <v>18.40749734138276</v>
+        <v>2.991218317974699</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.79540965010675</v>
+        <v>5.654254068142347</v>
       </c>
       <c r="D3" t="n">
-        <v>35.89675751323789</v>
+        <v>5.833223095901157</v>
       </c>
       <c r="E3" t="n">
-        <v>18.02622227559591</v>
+        <v>2.929261119784336</v>
       </c>
       <c r="F3" t="n">
-        <v>18.40749734138276</v>
+        <v>2.991218317974699</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>78.933361247234</v>
+        <v>12.82667120267553</v>
       </c>
       <c r="D4" t="n">
-        <v>80.74074420026415</v>
+        <v>13.12037093254292</v>
       </c>
       <c r="E4" t="n">
-        <v>18.02622227559591</v>
+        <v>2.929261119784336</v>
       </c>
       <c r="F4" t="n">
-        <v>18.40749734138276</v>
+        <v>2.991218317974699</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
